--- a/Special Course/Excel/Senior/материалы/Сотрудники.xlsx
+++ b/Special Course/Excel/Senior/материалы/Сотрудники.xlsx
@@ -428,7 +428,7 @@
   <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
@@ -465,196 +465,196 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Кузнецова Ольга Сергеевна </t>
+          <t xml:space="preserve">  Смирнов Иван Иванович </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07.09.2023</t>
+          <t>06.07.2021</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>89546890476</t>
+          <t>+7 (997) 737-65-62</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ольга.кузнецова@company.ru</t>
+          <t>иван.смирнов@company.ru</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Смирнов Сергей Сергеевич</t>
+          <t xml:space="preserve">   Кузнецов Николай Александрович </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25.03.2016</t>
+          <t>13.12.2017</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7 990 9289908</t>
+          <t>+7 (950) 705-15-45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>сергей.смирнов@company.ru</t>
+          <t>николай.кузнецов@company.ru</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Новикова Ирина Петровна</t>
+          <t>Смирнов  Иван Дмитриевич</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Бухгалтерия</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11.11.2020</t>
+          <t>14.03.2016</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+7 (929) 837-79-95</t>
+          <t>7 967 9597330</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ирина.новикова@company.ru</t>
+          <t>иван.смирнов@company.ru</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Смирнов Дмитрий Петрович </t>
+          <t>Волков Пётр Александрович</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15.08.2019</t>
+          <t>10.01.2021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+79141954456</t>
+          <t>+7 (962) 750-61-96</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>дмитрий.смирнов@company.ru</t>
+          <t>пётр.волков@company.ru</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Петров Пётр Петрович</t>
+          <t xml:space="preserve">  Кузнецова Наталья Петровна </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>02.12.2023</t>
+          <t>10.05.2017</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+79674158134</t>
+          <t>89449273246</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>пётр.петров@company.ru</t>
+          <t>наталья.кузнецова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Сидоров Александр Иванович </t>
+          <t>Смирнов  Иван Дмитриевич</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Бухгалтерия</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>03.12.2020</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+7 (974) 389-50-58</t>
+          <t>89909318184</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>александр.сидоров@company.ru</t>
+          <t>иван.смирнов@company.ru</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Новикова Наталья Петровна</t>
+          <t>Смирнов Александр Иванович</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14.07.2019</t>
+          <t>11.08.2020</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+79531878547</t>
+          <t>+79653283789</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>наталья.новикова@company.ru</t>
+          <t>александр.смирнов@company.ru</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Морозов Дмитрий Дмитриевич</t>
+          <t xml:space="preserve">  Кузнецова Елена Дмитриевна </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -664,51 +664,51 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11.03.2024</t>
+          <t>24.05.2020</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+79203372774</t>
+          <t>89989237735</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>дмитрий.морозов@company.ru</t>
+          <t>елена.кузнецова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Морозова  Мария Петровна</t>
+          <t>Морозов  Дмитрий Александрович</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Бухгалтерия</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21.07.2023</t>
+          <t>22.03.2023</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>+7 (952) 314-40-23</t>
+          <t>7 980 1451577</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>мария.морозова@company.ru</t>
+          <t>дмитрий.морозов@company.ru</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Иванова Ольга Дмитриевна </t>
+          <t>Смирнов Николай Александрович</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -718,444 +718,444 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>08.04.2022</t>
+          <t>16.11.2021</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>+7 (927) 359-95-48</t>
+          <t>89276080688</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ольга.иванова@company.ru</t>
+          <t>николай.смирнов@company.ru</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Петрова Наталья Петровна</t>
+          <t>Морозова Елена Александровна</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11.11.2015</t>
+          <t>18.07.2024</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7 989 3198638</t>
+          <t>+7 (974) 801-79-21</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>наталья.петрова@company.ru</t>
+          <t>елена.морозова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Сидоров Николай Иванович </t>
+          <t>Петрова Анна Сергеевна</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Бухгалтерия</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20.08.2018</t>
+          <t>19.01.2024</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>89468531761</t>
+          <t>+79927704473</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>николай.сидоров@company.ru</t>
+          <t>анна.петрова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Новиков Сергей Дмитриевич</t>
+          <t>Петров Дмитрий Сергеевич</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Бухгалтерия</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>25.08.2022</t>
+          <t>19.12.2024</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7 946 7406756</t>
+          <t>+79388478923</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>сергей.новиков@company.ru</t>
+          <t>дмитрий.петров@company.ru</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Сидорова Ольга Александровна</t>
+          <t>Сидоров Дмитрий Александрович</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23.02.2023</t>
+          <t>27.02.2016</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+79763091745</t>
+          <t>+79286843985</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ольга.сидорова@company.ru</t>
+          <t>дмитрий.сидоров@company.ru</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Смирнова Елена Петровна </t>
+          <t>Кузнецов  Пётр Иванович</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Бухгалтерия</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12.08.2018</t>
+          <t>03.06.2022</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>+7 (913) 796-08-15</t>
+          <t>+7 (948) 174-96-57</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>елена.смирнова@company.ru</t>
+          <t>пётр.кузнецов@company.ru</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Кузнецова  Елена Александровна</t>
+          <t>Петрова Ирина Сергеевна</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Бухгалтерия</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21.12.2016</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>89523450300</t>
+          <t>7 930 6553084</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>елена.кузнецова@company.ru</t>
+          <t>ирина.петрова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Новиков Николай Сергеевич</t>
+          <t xml:space="preserve">  Морозов Николай Сергеевич </t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>03.01.2024</t>
+          <t>24.01.2021</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>89125293691</t>
+          <t>7 988 4310554</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>николай.новиков@company.ru</t>
+          <t>николай.морозов@company.ru</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Морозова Анна Дмитриевна </t>
+          <t xml:space="preserve">  Иванов Николай Сергеевич </t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21.07.2018</t>
+          <t>04.10.2016</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>+7 (989) 866-90-93</t>
+          <t>+79784136665</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>анна.морозова@company.ru</t>
+          <t>николай.иванов@company.ru</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Новикова Наталья Петровна </t>
+          <t>Петров Дмитрий Иванович</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>05.12.2018</t>
+          <t>20.07.2024</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>+7 (947) 820-14-33</t>
+          <t>+79602916496</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>наталья.новикова@company.ru</t>
+          <t>дмитрий.петров@company.ru</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Морозов Сергей Александрович</t>
+          <t>Сидорова Ирина Дмитриевна</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Бухгалтерия</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17.09.2023</t>
+          <t>04.06.2017</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7 974 1341153</t>
+          <t>+7 (940) 612-34-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>сергей.морозов@company.ru</t>
+          <t>ирина.сидорова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Морозов Дмитрий Дмитриевич</t>
+          <t>Сидоров  Пётр Иванович</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Бухгалтерия</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>08.06.2016</t>
+          <t>06.07.2021</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>+79942739191</t>
+          <t>89723906397</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>дмитрий.морозов@company.ru</t>
+          <t>пётр.сидоров@company.ru</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Волков Николай Сергеевич</t>
+          <t>Сидоров Дмитрий Иванович</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Бухгалтерия</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>06.11.2022</t>
+          <t>05.08.2015</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7 927 2058651</t>
+          <t>7 934 7441514</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>николай.волков@company.ru</t>
+          <t>дмитрий.сидоров@company.ru</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Иванов Сергей Александрович</t>
+          <t>Морозова  Ирина Ивановна</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16.09.2021</t>
+          <t>10.04.2015</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>89421614394</t>
+          <t>89145611266</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>сергей.иванов@company.ru</t>
+          <t>ирина.морозова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Иванов Николай Дмитриевич </t>
+          <t>Новиков  Пётр Иванович</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Бухгалтерия</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>24.07.2021</t>
+          <t>25.05.2016</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>+79667486822</t>
+          <t>+7 (979) 715-49-19</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>николай.иванов@company.ru</t>
+          <t>пётр.новиков@company.ru</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Новиков Дмитрий Петрович </t>
+          <t xml:space="preserve">  Морозова Анна Сергеевна </t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14.02.2021</t>
+          <t>12.05.2022</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>+79874027557</t>
+          <t>+7 (921) 836-63-70</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>дмитрий.новиков@company.ru</t>
+          <t>анна.морозова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Волков Николай Дмитриевич</t>
+          <t>Волков  Николай Петрович</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>23.03.2021</t>
+          <t>27.04.2017</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7 966 6897979</t>
+          <t>+79361995859</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1167,61 +1167,61 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Волкова Наталья Ивановна </t>
+          <t xml:space="preserve">  Сидоров Дмитрий Дмитриевич </t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22.02.2015</t>
+          <t>27.11.2023</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>+79917815076</t>
+          <t>7 922 3274804</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>наталья.волкова@company.ru</t>
+          <t>дмитрий.сидоров@company.ru</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Сидорова Анна Сергеевна</t>
+          <t xml:space="preserve">  Сидорова Ирина Сергеевна </t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Бухгалтерия</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>05.01.2022</t>
+          <t>13.11.2018</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>+79184959345</t>
+          <t>+79723385244</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>анна.сидорова@company.ru</t>
+          <t>ирина.сидорова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Иванов Пётр Сергеевич</t>
+          <t>Петров Николай Александрович</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1231,132 +1231,132 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>25.08.2020</t>
+          <t>16.08.2020</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>+79193310140</t>
+          <t>+7 (951) 104-14-91</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>пётр.иванов@company.ru</t>
+          <t>николай.петров@company.ru</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Смирнов Сергей Александрович </t>
+          <t>Волкова Анна Петровна</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Бухгалтерия</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18.07.2023</t>
+          <t>09.08.2018</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>+79255391883</t>
+          <t>+79515757902</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>сергей.смирнов@company.ru</t>
+          <t>анна.волкова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Смирнов Николай Иванович </t>
+          <t xml:space="preserve">  Новикова Ольга Александровна </t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>06.08.2016</t>
+          <t>04.01.2022</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>+79662472884</t>
+          <t>7 930 8403549</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>николай.смирнов@company.ru</t>
+          <t>ольга.новикова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Смирнова Ольга Сергеевна</t>
+          <t>Морозова Мария Сергеевна</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17.06.2017</t>
+          <t>21.02.2019</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>89383036124</t>
+          <t>+7 (956) 520-08-35</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ольга.смирнова@company.ru</t>
+          <t>мария.морозова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Новиков Александр Дмитриевич</t>
+          <t>Сидорова Анна Ивановна</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Бухгалтерия</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20.03.2023</t>
+          <t>21.07.2018</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>+79212103070</t>
+          <t>+7 (921) 259-69-17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>александр.новиков@company.ru</t>
+          <t>анна.сидорова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Новикова Наталья Ивановна</t>
+          <t>Сидоров Пётр Сергеевич</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1366,78 +1366,78 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>11.03.2016</t>
+          <t>11.12.2015</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7 992 2244282</t>
+          <t>89258085252</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>наталья.новикова@company.ru</t>
+          <t>пётр.сидоров@company.ru</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Волкова  Мария Петровна</t>
+          <t xml:space="preserve">  Морозов Александр Александрович </t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>17.07.2017</t>
+          <t>13.03.2019</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>89173083077</t>
+          <t>+7 (927) 339-66-76</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>мария.волкова@company.ru</t>
+          <t>александр.морозов@company.ru</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Волков Николай Сергеевич</t>
+          <t>Сидорова Елена Дмитриевна</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>09.02.2019</t>
+          <t>20.07.2017</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>89355604524</t>
+          <t>89978421969</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>николай.волков@company.ru</t>
+          <t>елена.сидорова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Петрова Наталья Сергеевна</t>
+          <t>Сидорова Анна Петровна</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1447,24 +1447,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20.11.2017</t>
+          <t>26.06.2021</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>+7 (987) 666-43-16</t>
+          <t>+79275157165</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>наталья.петрова@company.ru</t>
+          <t>анна.сидорова@company.ru</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Смирнов Николай Сергеевич</t>
+          <t>Смирнов Николай Александрович</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1474,12 +1474,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>21.08.2015</t>
+          <t>17.04.2019</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>+79795859883</t>
+          <t>89879548370</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1491,54 +1491,54 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Морозов Дмитрий Иванович </t>
+          <t>Иванов Сергей Иванович</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>16.07.2022</t>
+          <t>17.02.2024</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>+79694422938</t>
+          <t>+79117058222</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>дмитрий.морозов@company.ru</t>
+          <t>сергей.иванов@company.ru</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Волков  Николай Дмитриевич</t>
+          <t>Морозов Дмитрий Петрович</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Бухгалтерия</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>18.09.2020</t>
+          <t>19.01.2016</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>89236353876</t>
+          <t>+79181231415</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>николай.волков@company.ru</t>
+          <t>дмитрий.морозов@company.ru</t>
         </is>
       </c>
     </row>
